--- a/data/trans_dic/P04D$individual-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 23,06</t>
+          <t>17,64; 23,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 19,61</t>
+          <t>14,28; 19,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 15,42</t>
+          <t>10,18; 15,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,49; 22,8</t>
+          <t>18,47; 22,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,12; 23,71</t>
+          <t>18,39; 23,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 11,73</t>
+          <t>8,2; 11,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,75; 22,19</t>
+          <t>18,71; 22,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,2</t>
+          <t>17,35; 21,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 12,74</t>
+          <t>9,37; 12,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 33,27</t>
+          <t>29,06; 33,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,6; 32,69</t>
+          <t>28,66; 32,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 49,04</t>
+          <t>16,68; 50,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,83; 33,4</t>
+          <t>28,96; 33,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,85; 36,27</t>
+          <t>31,89; 36,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 16,48</t>
+          <t>10,38; 16,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,63; 32,68</t>
+          <t>29,62; 32,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,87; 33,71</t>
+          <t>30,84; 33,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 34,1</t>
+          <t>15,13; 34,25</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,55; 48,44</t>
+          <t>38,14; 47,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,32; 41,4</t>
+          <t>32,74; 41,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 29,43</t>
+          <t>21,62; 29,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,66; 45,46</t>
+          <t>35,01; 45,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,66; 42,42</t>
+          <t>33,7; 41,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,34; 29,42</t>
+          <t>23,21; 29,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,33; 45,23</t>
+          <t>38,18; 45,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,33; 40,28</t>
+          <t>34,3; 40,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,42; 28,07</t>
+          <t>23,65; 28,44</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 31,31</t>
+          <t>28,11; 31,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,94; 30,12</t>
+          <t>27,06; 30,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,77; 43,9</t>
+          <t>17,92; 42,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,79; 29,89</t>
+          <t>26,75; 29,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,35; 32,6</t>
+          <t>29,22; 32,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,1</t>
+          <t>12,72; 17,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 30,31</t>
+          <t>27,86; 30,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,77; 31,07</t>
+          <t>28,61; 30,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,43; 30,88</t>
+          <t>16,29; 28,66</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>173347; 224349</t>
+          <t>171547; 224352</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107172; 147936</t>
+          <t>107717; 145310</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51422; 79077</t>
+          <t>52241; 79103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>247332; 305037</t>
+          <t>247026; 305955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>180278; 235868</t>
+          <t>182869; 235142</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61901; 88575</t>
+          <t>61909; 86979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>433266; 512674</t>
+          <t>432370; 512664</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>299430; 370734</t>
+          <t>303407; 371542</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120705; 161555</t>
+          <t>118787; 157725</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>918977</t>
+          <t>918978</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>568356; 651700</t>
+          <t>569145; 656831</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>593809; 678744</t>
+          <t>595116; 679906</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>378599; 1121251</t>
+          <t>381405; 1144894</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505484; 585716</t>
+          <t>507898; 589311</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>633261; 721174</t>
+          <t>634146; 720271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>231373; 368036</t>
+          <t>231738; 369001</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1100055; 1213110</t>
+          <t>1099704; 1216009</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1254676; 1370094</t>
+          <t>1253508; 1374992</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>689545; 1541014</t>
+          <t>683512; 1547823</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>185504; 233071</t>
+          <t>183537; 229713</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>176735; 226425</t>
+          <t>179039; 224699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143246; 190311</t>
+          <t>139831; 188214</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163527; 208484</t>
+          <t>160556; 208512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>184837; 232925</t>
+          <t>185088; 230599</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>153673; 193698</t>
+          <t>152776; 193114</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>360249; 425037</t>
+          <t>358819; 424221</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>376317; 441441</t>
+          <t>375952; 441947</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>305668; 366246</t>
+          <t>308665; 371133</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>958811; 1068667</t>
+          <t>959363; 1068243</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>909971; 1017363</t>
+          <t>913816; 1023601</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>612407; 1512570</t>
+          <t>617522; 1457127</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>951011; 1061096</t>
+          <t>949606; 1058428</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1036809; 1151319</t>
+          <t>1032092; 1147592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>458035; 623472</t>
+          <t>463647; 621863</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1940384; 2110292</t>
+          <t>1939503; 2097597</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1987661; 2146987</t>
+          <t>1977026; 2127141</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1165073; 2190176</t>
+          <t>1155482; 2032332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$individual-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 23,07</t>
+          <t>17,49; 22,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 19,26</t>
+          <t>14,22; 19,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,42</t>
+          <t>9,52; 15,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 22,87</t>
+          <t>18,5; 22,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,64</t>
+          <t>18,58; 23,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 11,52</t>
+          <t>7,84; 11,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 22,19</t>
+          <t>18,86; 22,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 21,24</t>
+          <t>17,37; 21,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 12,44</t>
+          <t>9,14; 12,18</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,06; 33,53</t>
+          <t>29,23; 33,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,66; 32,74</t>
+          <t>28,77; 32,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 50,08</t>
+          <t>15,1; 19,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,96; 33,61</t>
+          <t>28,97; 33,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,89; 36,23</t>
+          <t>32,01; 36,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,53</t>
+          <t>14,59; 17,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,62; 32,76</t>
+          <t>29,76; 32,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,84; 33,83</t>
+          <t>30,88; 33,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 34,25</t>
+          <t>15,41; 17,72</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,14; 47,74</t>
+          <t>38,08; 47,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,74; 41,09</t>
+          <t>32,34; 41,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,62; 29,11</t>
+          <t>21,73; 28,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,01; 45,46</t>
+          <t>35,22; 45,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,7; 41,99</t>
+          <t>33,65; 42,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 29,34</t>
+          <t>23,77; 29,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,18; 45,14</t>
+          <t>38,59; 45,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,3; 40,32</t>
+          <t>34,39; 40,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,65; 28,44</t>
+          <t>23,67; 28,13</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,11; 31,3</t>
+          <t>28,01; 31,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,06; 30,31</t>
+          <t>27,04; 30,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 42,29</t>
+          <t>16,34; 19,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 29,81</t>
+          <t>26,68; 29,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,22; 32,49</t>
+          <t>29,38; 32,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 17,06</t>
+          <t>15,46; 17,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,86; 30,13</t>
+          <t>27,82; 30,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,61; 30,78</t>
+          <t>28,71; 31,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,29; 28,66</t>
+          <t>16,4; 18,23</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73962</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138199</t>
+          <t>148209</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>171547; 224352</t>
+          <t>170094; 223229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107717; 145310</t>
+          <t>107266; 150057</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52241; 79103</t>
+          <t>54874; 87007</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>247026; 305955</t>
+          <t>247438; 307389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182869; 235142</t>
+          <t>184771; 238614</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61909; 86979</t>
+          <t>64392; 90450</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>432370; 512664</t>
+          <t>435811; 516876</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>303407; 371542</t>
+          <t>303727; 372536</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118787; 157725</t>
+          <t>127722; 170232</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>600102</t>
+          <t>379258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>318876</t>
+          <t>345336</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>918978</t>
+          <t>724594</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>569145; 656831</t>
+          <t>572518; 656264</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>595116; 679906</t>
+          <t>597324; 682853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>381405; 1144894</t>
+          <t>335678; 424528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>507898; 589311</t>
+          <t>507977; 583249</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>634146; 720271</t>
+          <t>636410; 724297</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>231738; 369001</t>
+          <t>315938; 379059</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1099704; 1216009</t>
+          <t>1104918; 1218998</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1253508; 1374992</t>
+          <t>1255038; 1373880</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>683512; 1547823</t>
+          <t>676536; 777902</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164628</t>
+          <t>176629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>173286</t>
+          <t>194798</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>337915</t>
+          <t>371427</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>183537; 229713</t>
+          <t>183231; 228974</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>179039; 224699</t>
+          <t>176873; 226029</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139831; 188214</t>
+          <t>154660; 204281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160556; 208512</t>
+          <t>161552; 206692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>185088; 230599</t>
+          <t>184759; 231502</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152776; 193114</t>
+          <t>173958; 216911</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>358819; 424221</t>
+          <t>362662; 425354</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>375952; 441947</t>
+          <t>376961; 444667</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>308665; 371133</t>
+          <t>341584; 405966</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828967</t>
+          <t>626486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>566124</t>
+          <t>617744</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1395091</t>
+          <t>1244230</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>959363; 1068243</t>
+          <t>956044; 1070480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>913816; 1023601</t>
+          <t>913187; 1016860</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>617522; 1457127</t>
+          <t>573629; 682473</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>949606; 1058428</t>
+          <t>947091; 1058387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1032092; 1147592</t>
+          <t>1037862; 1148511</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>463647; 621863</t>
+          <t>574952; 658238</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1939503; 2097597</t>
+          <t>1937323; 2094777</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1977026; 2127141</t>
+          <t>1983790; 2143682</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1155482; 2032332</t>
+          <t>1185671; 1318201</t>
         </is>
       </c>
     </row>
